--- a/Result/profitability/9914.xlsx
+++ b/Result/profitability/9914.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.12</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03874999999999981</v>
+        <v>-0.1175000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>14.80875</v>
+        <v>14.77625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.42</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07250000000000023</v>
+        <v>1.08875</v>
       </c>
       <c r="N3" t="n">
-        <v>14.5125</v>
+        <v>15.07375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13375</v>
+        <v>1.09125</v>
       </c>
       <c r="N4" t="n">
-        <v>14.65</v>
+        <v>14.82875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1525</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>14.54375</v>
+        <v>14.935</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.155</v>
+        <v>1.02625</v>
       </c>
       <c r="N6" t="n">
-        <v>14.1375</v>
+        <v>14.685</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>1.085</v>
+        <v>1.31625</v>
       </c>
       <c r="N7" t="n">
-        <v>14.31875</v>
+        <v>15.31375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>1.48</v>
       </c>
       <c r="M8" t="n">
-        <v>1.36875</v>
+        <v>1.365</v>
       </c>
       <c r="N8" t="n">
-        <v>14.7725</v>
+        <v>14.945</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9914</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6939</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5691</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1248</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="G75" t="n">
+        <v>765</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.03%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-303</v>
+      </c>
+      <c r="J75" t="n">
+        <v>462</v>
+      </c>
+      <c r="K75" t="n">
+        <v>318</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.03124999999999981</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.16625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.02752293577981657</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.379999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08313253012048194</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.196969696969697</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.130000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2107744107744107</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
